--- a/data/trans_orig/IP04D$colectiva-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$colectiva-Provincia-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>561</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52482</t>
+          <t>52926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62375</t>
+          <t>61558</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116621</t>
+          <t>116629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120716</t>
+          <t>120706</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99224</t>
+          <t>98807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103477</t>
+          <t>103476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102735</t>
+          <t>102692</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108606</t>
+          <t>108632</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>204263</t>
+          <t>203638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211405</t>
+          <t>211400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>625</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63511</t>
+          <t>63271</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67019</t>
+          <t>67737</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133609</t>
+          <t>133352</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138808</t>
+          <t>138807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>15976</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65857</t>
+          <t>65938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74684</t>
+          <t>74878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73910</t>
+          <t>73856</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81526</t>
+          <t>81521</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145097</t>
+          <t>144019</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155302</t>
+          <t>155198</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>16874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35188</t>
+          <t>35434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42290</t>
+          <t>42349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>35180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43614</t>
+          <t>43354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>73838</t>
+          <t>73779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>84346</t>
+          <t>84392</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10488</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>53881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54680</t>
+          <t>53689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59545</t>
+          <t>59529</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105048</t>
+          <t>104590</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>112653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>131658</t>
+          <t>131937</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>138018</t>
+          <t>138023</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142351</t>
+          <t>142322</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277565</t>
+          <t>276957</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283746</t>
+          <t>283647</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>155919</t>
+          <t>156411</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>162509</t>
+          <t>162568</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162476</t>
+          <t>162105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169780</t>
+          <t>169787</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>321016</t>
+          <t>321527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>330700</t>
+          <t>330875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17982</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>32935</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15008</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35902</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>58113</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>673894</t>
+          <t>675357</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>690310</t>
+          <t>690852</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>722190</t>
+          <t>723178</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>737217</t>
+          <t>737948</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1403167</t>
+          <t>1402404</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1424615</t>
+          <t>1425888</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4634</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101017</t>
+          <t>100959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106155</t>
+          <t>105649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208647</t>
+          <t>208525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213664</t>
+          <t>213666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61673</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66185</t>
+          <t>66169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64540</t>
+          <t>64551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69261</t>
+          <t>69256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>128407</t>
+          <t>128472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135296</t>
+          <t>134794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4342</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68064</t>
+          <t>68510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74704</t>
+          <t>74676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71784</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78914</t>
+          <t>79577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142469</t>
+          <t>142954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>152968</t>
+          <t>152849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15925</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7419</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17508</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30279</t>
+          <t>30361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>47821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>39768</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50320</t>
+          <t>50427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81733</t>
+          <t>81651</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>96031</t>
+          <t>95894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,61%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>17452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>126158</t>
+          <t>126352</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>134067</t>
+          <t>133914</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130709</t>
+          <t>130209</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137848</t>
+          <t>137827</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>259594</t>
+          <t>259060</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270295</t>
+          <t>270181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158667</t>
+          <t>158584</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163639</t>
+          <t>163641</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>165411</t>
+          <t>165291</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>326683</t>
+          <t>326490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>333120</t>
+          <t>333131</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19382</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35710</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40111</t>
+          <t>40100</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64109</t>
+          <t>63666</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>666314</t>
+          <t>665729</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>682789</t>
+          <t>682158</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>704301</t>
+          <t>704642</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>720629</t>
+          <t>721497</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1376083</t>
+          <t>1376526</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1400081</t>
+          <t>1400092</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6359</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5896</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70764</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>74325</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146752</t>
+          <t>147105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>840</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>119681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126826</t>
+          <t>126814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120798</t>
+          <t>121028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>244662</t>
+          <t>244306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253286</t>
+          <t>253336</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27033</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46633</t>
+          <t>46612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54163</t>
+          <t>54575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48596</t>
+          <t>48807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59144</t>
+          <t>59531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>98398</t>
+          <t>98796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111863</t>
+          <t>112043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54247</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63776</t>
+          <t>64386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69414</t>
+          <t>69269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77179</t>
+          <t>77342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>127884</t>
+          <t>127974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140329</t>
+          <t>140315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15090</t>
+          <t>14934</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33178</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48313</t>
+          <t>47771</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,67%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20733</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>31233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30031</t>
+          <t>29770</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40957</t>
+          <t>41592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54040</t>
+          <t>54582</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69175</t>
+          <t>69707</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>68,1%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20486</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18566</t>
+          <t>18673</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34737</t>
+          <t>35611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>105742</t>
+          <t>105734</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>117322</t>
+          <t>117231</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134583</t>
+          <t>134254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>146955</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244840</t>
+          <t>243966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261011</t>
+          <t>260904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>152647</t>
+          <t>152830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>284544</t>
+          <t>284626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>41031</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64809</t>
+          <t>64200</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>42303</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>65804</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87935</t>
+          <t>89985</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>122650</t>
+          <t>122939</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>600347</t>
+          <t>600956</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>623672</t>
+          <t>624125</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>694359</t>
+          <t>694518</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>718019</t>
+          <t>719246</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1302827</t>
+          <t>1302538</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1337542</t>
+          <t>1335492</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
